--- a/exam.xlsx
+++ b/exam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faycal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F6E8F3-D1B6-42A2-9924-6FC5AA723318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A239A39-13D1-4639-86D7-0CE90E692C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -376,7 +376,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -464,9 +464,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
@@ -814,7 +811,7 @@
       <c r="B2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="32">
+      <c r="C2" s="31">
         <v>120203</v>
       </c>
       <c r="D2" s="10" t="s">
@@ -854,7 +851,7 @@
       <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="31">
         <v>120217</v>
       </c>
       <c r="D3" s="10" t="s">
@@ -894,7 +891,7 @@
       <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="31">
         <v>120238</v>
       </c>
       <c r="D4" s="11" t="s">
@@ -934,7 +931,7 @@
       <c r="B5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="31">
         <v>119870</v>
       </c>
       <c r="D5" s="10" t="s">
@@ -974,7 +971,7 @@
       <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="31">
         <v>120087</v>
       </c>
       <c r="D6" s="12" t="s">
@@ -1014,7 +1011,7 @@
       <c r="B7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="31">
         <v>119935</v>
       </c>
       <c r="D7" s="13" t="s">
@@ -1054,7 +1051,7 @@
       <c r="B8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="31">
         <v>120239</v>
       </c>
       <c r="D8" s="14" t="s">
@@ -1094,7 +1091,7 @@
       <c r="B9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="31">
         <v>120240</v>
       </c>
       <c r="D9" s="10" t="s">
@@ -1134,7 +1131,7 @@
       <c r="B10" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="32">
+      <c r="C10" s="31">
         <v>120159</v>
       </c>
       <c r="D10" s="15" t="s">
@@ -1174,7 +1171,7 @@
       <c r="B11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="31">
         <v>120107</v>
       </c>
       <c r="D11" s="16" t="s">
@@ -1214,7 +1211,7 @@
       <c r="B12" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="32">
+      <c r="C12" s="31">
         <v>120227</v>
       </c>
       <c r="D12" s="16" t="s">
@@ -1494,10 +1491,12 @@
       <c r="A21" s="4">
         <v>46093</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="22"/>
+      <c r="C21" s="8">
+        <v>120259</v>
+      </c>
       <c r="D21" s="23" t="s">
         <v>27</v>
       </c>
@@ -1530,10 +1529,12 @@
       <c r="A22" s="4">
         <v>46093</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="22"/>
+      <c r="C22" s="8">
+        <v>120265</v>
+      </c>
       <c r="D22" s="23" t="s">
         <v>28</v>
       </c>
@@ -1566,10 +1567,12 @@
       <c r="A23" s="4">
         <v>46093</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="22"/>
+      <c r="C23" s="8">
+        <v>120012</v>
+      </c>
       <c r="D23" s="21" t="s">
         <v>29</v>
       </c>
@@ -1602,10 +1605,12 @@
       <c r="A24" s="4">
         <v>46093</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="22"/>
+      <c r="C24" s="8">
+        <v>120275</v>
+      </c>
       <c r="D24" s="23" t="s">
         <v>30</v>
       </c>
@@ -1638,10 +1643,12 @@
       <c r="A25" s="4">
         <v>46093</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="22"/>
+      <c r="C25" s="8">
+        <v>120283</v>
+      </c>
       <c r="D25" s="23" t="s">
         <v>31</v>
       </c>

--- a/exam.xlsx
+++ b/exam.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faycal\Desktop\exam results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\faycal\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54CC6B9E-D270-4063-ADCF-B068B8EEADB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{226CEF9D-4695-4A50-B93D-064017EC070D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,29 +37,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="34">
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>Stone#1</t>
-  </si>
-  <si>
     <t>Marks</t>
   </si>
   <si>
-    <t>Stone#2</t>
-  </si>
-  <si>
-    <t>Stone#3</t>
-  </si>
-  <si>
-    <t>Stone#4</t>
-  </si>
-  <si>
-    <t>Stone#5</t>
-  </si>
-  <si>
     <t>Theory</t>
   </si>
   <si>
@@ -71,9 +57,6 @@
     <t>Elena Garas</t>
   </si>
   <si>
-    <t>pass</t>
-  </si>
-  <si>
     <t>Acenath Faheem</t>
   </si>
   <si>
@@ -114,6 +97,48 @@
   </si>
   <si>
     <t>ID</t>
+  </si>
+  <si>
+    <t>Lorena Ospina Calderon</t>
+  </si>
+  <si>
+    <t>Abdennour Amine Idrissi</t>
+  </si>
+  <si>
+    <t>Zineb Amine Idrissi</t>
+  </si>
+  <si>
+    <t>Meriem Amine Idrissi</t>
+  </si>
+  <si>
+    <t>Sorting</t>
+  </si>
+  <si>
+    <t>RDG</t>
+  </si>
+  <si>
+    <t>PDG</t>
+  </si>
+  <si>
+    <t>Anastasiia Kupchak</t>
+  </si>
+  <si>
+    <t>Sabina Mamedova</t>
+  </si>
+  <si>
+    <t>Daria Bratkova</t>
+  </si>
+  <si>
+    <t>Arunraj Naduvathazhath Rajan</t>
+  </si>
+  <si>
+    <t>Sajed Hayder Atbi</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Oktay Kilic</t>
   </si>
 </sst>
 </file>
@@ -123,7 +148,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -161,8 +186,33 @@
       <name val="Century Gothic"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,8 +231,14 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -304,18 +360,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -334,9 +403,6 @@
     <xf numFmtId="10" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -346,7 +412,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -364,12 +430,53 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -647,671 +754,969 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.28515625" customWidth="1"/>
+    <col min="11" max="11" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>24</v>
+      <c r="B1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="M1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="4">
+        <v>46058</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="31">
+        <v>120203</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="E2" s="6">
+        <v>10</v>
+      </c>
+      <c r="F2" s="6">
+        <v>10</v>
+      </c>
+      <c r="G2" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="H2" s="6">
+        <v>7</v>
+      </c>
+      <c r="I2" s="6">
+        <v>10</v>
+      </c>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6">
+        <v>19</v>
+      </c>
+      <c r="L2" s="7">
+        <f t="shared" ref="L2:L12" si="0">SUM((E2+F2+G2+H2+I2+K2)/70)</f>
+        <v>0.93571428571428572</v>
+      </c>
+      <c r="M2" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A3" s="4">
+        <v>46058</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="31">
+        <v>120217</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="O1" s="3" t="s">
+      <c r="E3" s="6">
+        <v>10</v>
+      </c>
+      <c r="F3" s="6">
+        <v>10</v>
+      </c>
+      <c r="G3" s="6">
+        <v>9.75</v>
+      </c>
+      <c r="H3" s="6">
+        <v>10</v>
+      </c>
+      <c r="I3" s="6">
+        <v>10</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6">
+        <v>20</v>
+      </c>
+      <c r="L3" s="7">
+        <f t="shared" si="0"/>
+        <v>0.99642857142857144</v>
+      </c>
+      <c r="M3" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>46058</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="31">
+        <v>120238</v>
+      </c>
+      <c r="D4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="5">
-        <v>46058</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="19">
-        <v>111</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="6">
-        <v>6</v>
-      </c>
-      <c r="F2" s="7">
-        <v>10</v>
-      </c>
-      <c r="G2" s="6">
-        <v>12</v>
-      </c>
-      <c r="H2" s="7">
-        <v>10</v>
-      </c>
-      <c r="I2" s="6">
+      <c r="E4" s="6">
+        <v>10</v>
+      </c>
+      <c r="F4" s="6">
+        <v>10</v>
+      </c>
+      <c r="G4" s="6">
+        <v>9.5</v>
+      </c>
+      <c r="H4" s="6">
+        <v>10</v>
+      </c>
+      <c r="I4" s="6">
         <v>7</v>
       </c>
-      <c r="J2" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="K2" s="7">
-        <v>3</v>
-      </c>
-      <c r="L2" s="7">
-        <v>7</v>
-      </c>
-      <c r="M2" s="7">
-        <v>14</v>
-      </c>
-      <c r="N2" s="7">
-        <v>10</v>
-      </c>
-      <c r="O2" s="7">
-        <v>19</v>
-      </c>
-      <c r="P2" s="8">
-        <f>SUM((F2+H2+J2+L2+N2+O2)/70)</f>
-        <v>0.93571428571428572</v>
-      </c>
-      <c r="Q2" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="5">
-        <v>46058</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="19">
-        <v>222</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="6">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7">
-        <v>10</v>
-      </c>
-      <c r="G3" s="6">
-        <v>9</v>
-      </c>
-      <c r="H3" s="7">
-        <v>10</v>
-      </c>
-      <c r="I3" s="7">
-        <v>14</v>
-      </c>
-      <c r="J3" s="7">
-        <v>9.75</v>
-      </c>
-      <c r="K3" s="7">
-        <v>8</v>
-      </c>
-      <c r="L3" s="7">
-        <v>10</v>
-      </c>
-      <c r="M3" s="7">
-        <v>6</v>
-      </c>
-      <c r="N3" s="7">
-        <v>10</v>
-      </c>
-      <c r="O3" s="7">
-        <v>20</v>
-      </c>
-      <c r="P3" s="8">
-        <f t="shared" ref="P3:P12" si="0">SUM((F3+H3+J3+L3+N3+O3)/70)</f>
-        <v>0.99642857142857144</v>
-      </c>
-      <c r="Q3" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="5">
-        <v>46058</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="19">
-        <v>333</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="6">
-        <v>8</v>
-      </c>
-      <c r="F4" s="7">
-        <v>10</v>
-      </c>
-      <c r="G4" s="6">
-        <v>5</v>
-      </c>
-      <c r="H4" s="7">
-        <v>10</v>
-      </c>
-      <c r="I4" s="6">
-        <v>1</v>
-      </c>
-      <c r="J4" s="7">
-        <v>9.5</v>
-      </c>
+      <c r="J4" s="6"/>
       <c r="K4" s="6">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L4" s="7">
-        <v>10</v>
-      </c>
-      <c r="M4" s="6">
-        <v>10</v>
-      </c>
-      <c r="N4" s="7">
-        <v>7</v>
-      </c>
-      <c r="O4" s="7">
-        <v>18</v>
-      </c>
-      <c r="P4" s="8">
         <f t="shared" si="0"/>
         <v>0.92142857142857137</v>
       </c>
-      <c r="Q4" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
+      <c r="M4" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
         <v>46058</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="19">
-        <v>444</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>14</v>
+      <c r="B5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="31">
+        <v>119870</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>8</v>
       </c>
       <c r="E5" s="6">
-        <v>14</v>
-      </c>
-      <c r="F5" s="7">
         <v>9.75</v>
       </c>
+      <c r="F5" s="6">
+        <v>10</v>
+      </c>
       <c r="G5" s="6">
-        <v>8</v>
-      </c>
-      <c r="H5" s="7">
+        <v>10</v>
+      </c>
+      <c r="H5" s="6">
         <v>10</v>
       </c>
       <c r="I5" s="6">
-        <v>1</v>
-      </c>
-      <c r="J5" s="7">
-        <v>10</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="J5" s="6"/>
       <c r="K5" s="6">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L5" s="7">
-        <v>10</v>
-      </c>
-      <c r="M5" s="6">
-        <v>5</v>
-      </c>
-      <c r="N5" s="7">
-        <v>10</v>
-      </c>
-      <c r="O5" s="7">
-        <v>20</v>
-      </c>
-      <c r="P5" s="8">
         <f t="shared" si="0"/>
         <v>0.99642857142857144</v>
       </c>
-      <c r="Q5" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="M5" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
         <v>46058</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="19">
-        <v>555</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>15</v>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="31">
+        <v>120087</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>9</v>
       </c>
       <c r="E6" s="6">
-        <v>2</v>
-      </c>
-      <c r="F6" s="7">
         <v>8.5</v>
       </c>
+      <c r="F6" s="6">
+        <v>10</v>
+      </c>
       <c r="G6" s="6">
-        <v>7</v>
-      </c>
-      <c r="H6" s="7">
+        <v>8</v>
+      </c>
+      <c r="H6" s="6">
         <v>10</v>
       </c>
       <c r="I6" s="6">
-        <v>8</v>
-      </c>
-      <c r="J6" s="7">
-        <v>8</v>
-      </c>
+        <v>9.75</v>
+      </c>
+      <c r="J6" s="6"/>
       <c r="K6" s="6">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L6" s="7">
-        <v>10</v>
-      </c>
-      <c r="M6" s="6">
-        <v>13</v>
-      </c>
-      <c r="N6" s="7">
-        <v>9.75</v>
-      </c>
-      <c r="O6" s="7">
-        <v>20</v>
-      </c>
-      <c r="P6" s="8">
         <f t="shared" si="0"/>
         <v>0.9464285714285714</v>
       </c>
-      <c r="Q6" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
+      <c r="M6" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
         <v>46058</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="19">
-        <v>666</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>16</v>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="31">
+        <v>119935</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>10</v>
       </c>
       <c r="E7" s="6">
-        <v>6</v>
-      </c>
-      <c r="F7" s="7">
         <v>9.5</v>
       </c>
+      <c r="F7" s="6">
+        <v>10</v>
+      </c>
       <c r="G7" s="6">
-        <v>13</v>
-      </c>
-      <c r="H7" s="7">
+        <v>10</v>
+      </c>
+      <c r="H7" s="6">
         <v>10</v>
       </c>
       <c r="I7" s="6">
         <v>10</v>
       </c>
-      <c r="J7" s="7">
-        <v>10</v>
-      </c>
+      <c r="J7" s="6"/>
       <c r="K7" s="6">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L7" s="7">
-        <v>10</v>
-      </c>
-      <c r="M7" s="6">
-        <v>3</v>
-      </c>
-      <c r="N7" s="7">
-        <v>10</v>
-      </c>
-      <c r="O7" s="7">
-        <v>17</v>
-      </c>
-      <c r="P7" s="8">
         <f t="shared" si="0"/>
         <v>0.95</v>
       </c>
-      <c r="Q7" s="9" t="s">
+      <c r="M7" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>46058</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="31">
+        <v>120239</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>46058</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="19">
-        <v>777</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>17</v>
-      </c>
       <c r="E8" s="6">
         <v>10</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>10</v>
       </c>
       <c r="G8" s="6">
-        <v>12</v>
-      </c>
-      <c r="H8" s="7">
+        <v>10</v>
+      </c>
+      <c r="H8" s="6">
         <v>10</v>
       </c>
       <c r="I8" s="6">
-        <v>8</v>
-      </c>
-      <c r="J8" s="7">
-        <v>10</v>
-      </c>
+        <v>9.5</v>
+      </c>
+      <c r="J8" s="6"/>
       <c r="K8" s="6">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="L8" s="7">
-        <v>10</v>
-      </c>
-      <c r="M8" s="6">
-        <v>1</v>
-      </c>
-      <c r="N8" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="O8" s="7">
-        <v>19</v>
-      </c>
-      <c r="P8" s="8">
         <f t="shared" si="0"/>
         <v>0.97857142857142854</v>
       </c>
-      <c r="Q8" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
+      <c r="M8" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
         <v>46058</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="19">
-        <v>888</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>18</v>
+      <c r="B9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="31">
+        <v>120240</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>12</v>
       </c>
       <c r="E9" s="6">
-        <v>12</v>
-      </c>
-      <c r="F9" s="7">
         <v>9.5</v>
       </c>
+      <c r="F9" s="6">
+        <v>10</v>
+      </c>
       <c r="G9" s="6">
         <v>10</v>
       </c>
-      <c r="H9" s="7">
-        <v>10</v>
+      <c r="H9" s="6">
+        <v>9.5</v>
       </c>
       <c r="I9" s="6">
-        <v>11</v>
-      </c>
-      <c r="J9" s="7">
-        <v>10</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="J9" s="6"/>
       <c r="K9" s="6">
-        <v>2</v>
+        <v>17.5</v>
       </c>
       <c r="L9" s="7">
-        <v>9.5</v>
-      </c>
-      <c r="M9" s="6">
-        <v>4</v>
-      </c>
-      <c r="N9" s="7">
-        <v>7</v>
-      </c>
-      <c r="O9" s="7">
-        <v>17.5</v>
-      </c>
-      <c r="P9" s="8">
         <f t="shared" si="0"/>
         <v>0.90714285714285714</v>
       </c>
-      <c r="Q9" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="M9" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
         <v>46058</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="19">
-        <v>999</v>
-      </c>
-      <c r="D10" s="17" t="s">
+      <c r="B10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="31">
+        <v>120159</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="8">
+        <v>10</v>
+      </c>
+      <c r="F10" s="8">
+        <v>10</v>
+      </c>
+      <c r="G10" s="8">
+        <v>9.75</v>
+      </c>
+      <c r="H10" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="I10" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8">
         <v>19</v>
       </c>
-      <c r="E10" s="10">
-        <v>12</v>
-      </c>
-      <c r="F10" s="10">
-        <v>10</v>
-      </c>
-      <c r="G10" s="10">
-        <v>16</v>
-      </c>
-      <c r="H10" s="10">
-        <v>10</v>
-      </c>
-      <c r="I10" s="10">
-        <v>13</v>
-      </c>
-      <c r="J10" s="10">
-        <v>9.75</v>
-      </c>
-      <c r="K10" s="10">
-        <v>9</v>
-      </c>
-      <c r="L10" s="10">
-        <v>8.5</v>
-      </c>
-      <c r="M10" s="10">
-        <v>5</v>
-      </c>
-      <c r="N10" s="10">
-        <v>9.5</v>
-      </c>
-      <c r="O10" s="10">
-        <v>19</v>
-      </c>
-      <c r="P10" s="8">
+      <c r="L10" s="7">
         <f t="shared" si="0"/>
         <v>0.95357142857142863</v>
       </c>
-      <c r="Q10" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="5">
+      <c r="M10" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>46058</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="19">
-        <v>1010</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="10">
-        <v>11</v>
-      </c>
-      <c r="F11" s="10">
-        <v>10</v>
-      </c>
-      <c r="G11" s="10">
-        <v>6</v>
-      </c>
-      <c r="H11" s="10">
-        <v>10</v>
-      </c>
-      <c r="I11" s="10">
-        <v>7</v>
-      </c>
-      <c r="J11" s="10">
-        <v>10</v>
-      </c>
-      <c r="K11" s="10">
-        <v>2</v>
-      </c>
-      <c r="L11" s="10">
+      <c r="B11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="31">
+        <v>120107</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="8">
+        <v>10</v>
+      </c>
+      <c r="F11" s="8">
+        <v>10</v>
+      </c>
+      <c r="G11" s="8">
+        <v>10</v>
+      </c>
+      <c r="H11" s="8">
         <v>9.5</v>
       </c>
-      <c r="M11" s="10">
-        <v>1</v>
-      </c>
-      <c r="N11" s="10">
-        <v>10</v>
-      </c>
-      <c r="O11" s="10">
+      <c r="I11" s="8">
+        <v>10</v>
+      </c>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8">
         <v>19</v>
       </c>
-      <c r="P11" s="8">
+      <c r="L11" s="7">
         <f t="shared" si="0"/>
         <v>0.97857142857142854</v>
       </c>
-      <c r="Q11" s="9" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+      <c r="M11" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>46058</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="19">
-        <v>11011</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="10">
-        <v>16</v>
-      </c>
-      <c r="F12" s="10">
+      <c r="B12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="31">
+        <v>120227</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="8">
         <v>9.5</v>
       </c>
-      <c r="G12" s="10">
-        <v>7</v>
-      </c>
-      <c r="H12" s="10">
+      <c r="F12" s="8">
         <v>9.5</v>
       </c>
-      <c r="I12" s="10">
-        <v>13</v>
-      </c>
-      <c r="J12" s="10">
+      <c r="G12" s="8">
         <v>9.5</v>
       </c>
-      <c r="K12" s="10">
-        <v>12</v>
-      </c>
-      <c r="L12" s="10">
+      <c r="H12" s="8">
         <v>9.5</v>
       </c>
-      <c r="M12" s="10">
-        <v>1</v>
-      </c>
-      <c r="N12" s="10">
-        <v>10</v>
-      </c>
-      <c r="O12" s="10">
+      <c r="I12" s="8">
+        <v>10</v>
+      </c>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8">
         <v>20</v>
       </c>
-      <c r="P12" s="8">
+      <c r="L12" s="7">
         <f t="shared" si="0"/>
         <v>0.97142857142857142</v>
       </c>
-      <c r="Q12" s="9" t="s">
-        <v>11</v>
+      <c r="M12" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="30"/>
+    </row>
+    <row r="14" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="24">
+        <v>120156</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="17">
+        <v>9.25</v>
+      </c>
+      <c r="F14" s="17">
+        <v>8</v>
+      </c>
+      <c r="G14" s="17">
+        <v>9</v>
+      </c>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="17">
+        <v>7</v>
+      </c>
+      <c r="K14" s="17">
+        <v>17</v>
+      </c>
+      <c r="L14" s="25">
+        <f t="shared" ref="L14:L25" si="1">(E14+F14+G14+J14+K14)/60</f>
+        <v>0.83750000000000002</v>
+      </c>
+      <c r="M14" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" s="20">
+        <v>120087</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="17">
+        <v>9.5</v>
+      </c>
+      <c r="F15" s="17">
+        <v>9.5</v>
+      </c>
+      <c r="G15" s="17">
+        <v>9.5</v>
+      </c>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="17">
+        <v>9</v>
+      </c>
+      <c r="K15" s="17">
+        <v>20</v>
+      </c>
+      <c r="L15" s="25">
+        <f t="shared" si="1"/>
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="M15" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="20">
+        <v>120159</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="17">
+        <v>9</v>
+      </c>
+      <c r="F16" s="17">
+        <v>9</v>
+      </c>
+      <c r="G16" s="17">
+        <v>9</v>
+      </c>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="17">
+        <v>9</v>
+      </c>
+      <c r="K16" s="17">
+        <v>19</v>
+      </c>
+      <c r="L16" s="25">
+        <f t="shared" si="1"/>
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="M16" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="18">
+        <v>120098</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="17">
+        <v>9.5</v>
+      </c>
+      <c r="F17" s="17">
+        <v>7.5</v>
+      </c>
+      <c r="G17" s="17">
+        <v>8</v>
+      </c>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="17">
+        <v>7</v>
+      </c>
+      <c r="K17" s="17">
+        <v>18</v>
+      </c>
+      <c r="L17" s="25">
+        <f t="shared" si="1"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="M17" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="18">
+        <v>120100</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="17">
+        <v>9.5</v>
+      </c>
+      <c r="F18" s="17">
+        <v>9.5</v>
+      </c>
+      <c r="G18" s="17">
+        <v>9</v>
+      </c>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="17">
+        <v>8</v>
+      </c>
+      <c r="K18" s="17">
+        <v>18.5</v>
+      </c>
+      <c r="L18" s="25">
+        <f t="shared" si="1"/>
+        <v>0.90833333333333333</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="4">
+        <v>46009</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="18">
+        <v>120099</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="17">
+        <v>18</v>
+      </c>
+      <c r="F19" s="17">
+        <v>7</v>
+      </c>
+      <c r="G19" s="17">
+        <v>9</v>
+      </c>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
+      <c r="J19" s="17">
+        <v>8</v>
+      </c>
+      <c r="K19" s="17">
+        <v>7.5</v>
+      </c>
+      <c r="L19" s="25">
+        <f t="shared" si="1"/>
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="M19" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>46093</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="8">
+        <v>120259</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="8">
+        <v>7.9</v>
+      </c>
+      <c r="F21" s="8">
+        <v>9.56</v>
+      </c>
+      <c r="G21" s="8">
+        <v>8.67</v>
+      </c>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="8">
+        <v>10</v>
+      </c>
+      <c r="K21" s="8">
+        <v>19</v>
+      </c>
+      <c r="L21" s="25">
+        <f t="shared" si="1"/>
+        <v>0.91883333333333339</v>
+      </c>
+      <c r="M21" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
+        <v>46093</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="8">
+        <v>120265</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="8">
+        <v>9.34</v>
+      </c>
+      <c r="F22" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="G22" s="8">
+        <v>9.1</v>
+      </c>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="8">
+        <v>10</v>
+      </c>
+      <c r="K22" s="8">
+        <v>19</v>
+      </c>
+      <c r="L22" s="25">
+        <f t="shared" si="1"/>
+        <v>0.93233333333333335</v>
+      </c>
+      <c r="M22" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="4">
+        <v>46093</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23" s="8">
+        <v>120012</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="8">
+        <v>8.35</v>
+      </c>
+      <c r="F23" s="8">
+        <v>8</v>
+      </c>
+      <c r="G23" s="8">
+        <v>8.5</v>
+      </c>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8">
+        <v>10</v>
+      </c>
+      <c r="K23" s="8">
+        <v>19.5</v>
+      </c>
+      <c r="L23" s="25">
+        <f t="shared" si="1"/>
+        <v>0.90583333333333338</v>
+      </c>
+      <c r="M23" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="4">
+        <v>46093</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="8">
+        <v>120275</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="8">
+        <v>8.9</v>
+      </c>
+      <c r="F24" s="8">
+        <v>8.75</v>
+      </c>
+      <c r="G24" s="8">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8">
+        <v>7</v>
+      </c>
+      <c r="K24" s="8">
+        <v>17</v>
+      </c>
+      <c r="L24" s="25">
+        <f t="shared" si="1"/>
+        <v>0.83499999999999985</v>
+      </c>
+      <c r="M24" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>46093</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C25" s="8">
+        <v>120283</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="8">
+        <v>8</v>
+      </c>
+      <c r="F25" s="8">
+        <v>7</v>
+      </c>
+      <c r="G25" s="8">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="H25" s="8"/>
+      <c r="I25" s="8"/>
+      <c r="J25" s="8">
+        <v>9</v>
+      </c>
+      <c r="K25" s="8">
+        <v>17</v>
+      </c>
+      <c r="L25" s="25">
+        <f t="shared" si="1"/>
+        <v>0.83833333333333326</v>
+      </c>
+      <c r="M25" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>46114</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C27" s="8">
+        <v>120294</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="8">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="F27" s="8">
+        <v>9.34</v>
+      </c>
+      <c r="G27" s="8">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+      <c r="J27" s="8">
+        <v>10</v>
+      </c>
+      <c r="K27" s="8">
+        <v>18</v>
+      </c>
+      <c r="L27" s="25">
+        <f t="shared" ref="L27" si="2">(E27+F27+G27+J27+K27)/60</f>
+        <v>0.91516666666666657</v>
+      </c>
+      <c r="M27" s="19" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
